--- a/survey_templates/034_language_practice_survey--survey_templates.xlsx
+++ b/survey_templates/034_language_practice_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_templates_education_surveys</t>
+          <t>survey_questions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Education Surveys</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Language Learning Habits</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Describe your typical language learning activities</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>learner_habits</t>
+          <t>progress_tracking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>learner_habits</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Progress Tracking Method</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How do you keep track of your progress?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>learner_challenges</t>
+          <t>helpful_resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>learner_challenges</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Helpful Language Programs or Resources</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Which resources have you found most helpful?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -589,38 +601,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>progress</t>
+          <t>received_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>progress</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Received Support</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Have you ever received support from a language teacher or tutor?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>note_taking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Note Taking Method</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How do you take notes during language learning sessions?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,38 +655,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>language_programs</t>
+          <t>practice_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>language_programs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Practice Frequency</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How often do you practice writing or speaking a language for personal or professional purposes?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Output File</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Is there a specific output file for this survey?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Category Name</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>What category does this survey belong to?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Briefly describe the purpose of the survey</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,23 +758,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>form_ids</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Form IDs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter form IDs for this survey</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Which language learning tool was assigned for this survey?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,322 +812,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select the category for this survey</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>category_name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Category Name</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Form IDs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>category_name</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>category_name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,58 +875,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>survey_templates_education_surveys_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>calendar_or_planner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Calendar or planner</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>survey_templates_education_surveys_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mobile app</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_templates,_education_surveys</t>
+          <t>paper_notebook</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Templates, Education Surveys</t>
+          <t>Paper notebook</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,34 +943,204 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>helpful_resources_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>language_exchange_websites_(e.g.,_language_exchange_websites)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Language exchange websites (e.g., language exchange websites)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>helpful_resources_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>language_learning_apps_(e.g.,_duolingo,_babbel)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Language learning apps (e.g., Duolingo, Babbel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>helpful_resources_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>language_learning_podcasts_(e.g.,_6_minute_russian)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Language learning podcasts (e.g., 6 Minute Russian)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>helpful_resources_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>language_learning_youtube_channels_(e.g.,_english_class_101)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Language learning YouTube channels (e.g., English Class 101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>helpful_resources_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>note_taking_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>using_a_notebook_or_paper</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Using a notebook or paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>note_taking_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>using_a_digital_note-taking_app</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Using a digital note-taking app</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>note_taking_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>recording_audio_or_video</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Recording audio or video</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note_taking_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>not_taking_notes_at_all</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not taking notes at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>category_choices</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>survey_templates</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Survey Templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>category_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>education_surveys</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Education Surveys</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>category_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
